--- a/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
+++ b/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
@@ -3562,7 +3562,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
+          <t>CÔNG TY TNHH TƯ VẤN VÀ XÂY DỰNG DQT</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3578,7 +3578,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẠT LINH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3594,7 +3594,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TƯ VẤN VÀ XÂY DỰNG DQT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẠT LINH GIA LAI</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3962,7 +3962,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ KON GANG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG THƯƠNG MẠI VÀ DỊCH VỤ AN PHÚ</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3994,7 +3994,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG THƯƠNG MẠI VÀ DỊCH VỤ AN PHÚ</t>
+          <t>UỶ BAN NHÂN DÂN XÃ KON GANG</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4298,7 +4298,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐỨC DUNG - IAGRAI</t>
+          <t>TRUNG TÂM ỨNG DỤNG TIẾN BỘ KHOA HỌC VÀ CÔNG NGHỆ TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -4314,7 +4314,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TRUNG TÂM ỨNG DỤNG TIẾN BỘ KHOA HỌC VÀ CÔNG NGHỆ TỈNH GIA LAI</t>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐỨC DUNG - IAGRAI</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -4394,7 +4394,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ban quản lý dự án - Sư đoàn 320 / Quân đoàn 3</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ CHẾ BIẾN LOUIS DREYFUS COMPANY VIỆT NAM</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -4410,7 +4410,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ CHẾ BIẾN LOUIS DREYFUS COMPANY VIỆT NAM</t>
+          <t>Ban quản lý dự án - Sư đoàn 320 / Quân đoàn 3</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -5162,7 +5162,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẪU GIÁO SAO MAI</t>
+          <t>CÔNG TY CỔ PHẦN XÂY DỰNG 711</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -5178,7 +5178,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XÂY DỰNG 711</t>
+          <t>TRƯỜNG MẪU GIÁO SAO MAI</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -5530,7 +5530,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>LÊ THỊ LINH PHƯƠNG</t>
+          <t>Trại giống cây trồng - Binh đoàn 16</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -5546,7 +5546,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Trại giống cây trồng - Binh đoàn 16</t>
+          <t>LÊ THỊ LINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -5706,7 +5706,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV LÂM NGHIỆP KONG H'DE</t>
+          <t>ĐỒN BIÊN PHÒNG IA PNÔN</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -5722,7 +5722,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ĐỒN BIÊN PHÒNG IA PNÔN</t>
+          <t>CÔNG TY CỔ PHẦN VĂN HÓA GIÁO DỤC GIA LAI</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -5738,7 +5738,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VĂN HÓA GIÁO DỤC GIA LAI</t>
+          <t>CÔNG TY TNHH MTV LÂM NGHIỆP KONG H'DE</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -5834,7 +5834,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KIẾN TRÚC XÂY DỰNG TDH</t>
+          <t>Tiểu Đoàn Bộ Binh 50</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -5850,7 +5850,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Tiểu Đoàn Bộ Binh 50</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KIẾN TRÚC XÂY DỰNG TDH</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -6010,7 +6010,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HUẤN LUYỆN VÀ THI ĐẤU THỂ THAO TÍNH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TRƯỜNG THI GIA LAI</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -6026,7 +6026,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TRƯỜNG THI GIA LAI</t>
+          <t>TRUNG TÂM HUẤN LUYỆN VÀ THI ĐẤU THỂ THAO TÍNH</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -6138,7 +6138,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TRUNG ĐOÀN BỘ BINH 991</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP -GIÁO DỤC THƯỜNG XUYÊN HUYỆN ĐAK ĐOA</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -6170,7 +6170,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP -GIÁO DỤC THƯỜNG XUYÊN HUYỆN ĐAK ĐOA</t>
+          <t>TRUNG ĐOÀN BỘ BINH 991</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -6234,7 +6234,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM GIA HUY GL</t>
+          <t>LIÊN MINH HỢP TÁC XÃ TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -6250,7 +6250,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>LIÊN MINH HỢP TÁC XÃ TỈNH GIA LAI</t>
+          <t>CÔNG TY TNHH KIM GIA HUY GL</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -6362,7 +6362,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐĂK ĐOA</t>
+          <t>TRUNG ĐOÀN 48</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -6378,7 +6378,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>TRUNG ĐOÀN 48</t>
+          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐĂK ĐOA</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -6506,7 +6506,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HG AGRI</t>
+          <t>HOÀNG THỊ HỒNG MINH - CỬA HÀNG THƯƠNG MẠI VÀ DỊCH VỤ THIẾT BỊ VĂN PHÒNG MINH PHÁT</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -6522,7 +6522,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>HOÀNG THỊ HỒNG MINH - CỬA HÀNG THƯƠNG MẠI VÀ DỊCH VỤ THIẾT BỊ VĂN PHÒNG MINH PHÁT</t>
+          <t>CÔNG TY TNHH HG AGRI</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -7002,7 +7002,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -7018,7 +7018,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
+          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -7034,7 +7034,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ VPS</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -7050,7 +7050,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ VPS</t>
+          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -7114,7 +7114,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ANDRITZ VIỆT NAM</t>
+          <t>CÔNG TY TNHH HOÀNG AUTO GIA LAI</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -7146,7 +7146,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOÀNG AUTO GIA LAI</t>
+          <t>CÔNG TY TNHH ANDRITZ VIỆT NAM</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -7226,7 +7226,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THẨM ĐỊNH GIÁ VINACONTROL - TẠI ĐÀ NẴNG</t>
+          <t>Đồn Biên phòng Ia Lốp</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -7242,7 +7242,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Đồn Biên phòng Ia Lốp</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THẨM ĐỊNH GIÁ VINACONTROL - TẠI ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -7290,7 +7290,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>BAN DÂN TỘC TỈNH GIA LAI</t>
+          <t>UBND THỊ TRẤN KongChro</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -7306,7 +7306,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>UBND THỊ TRẤN KongChro</t>
+          <t>BAN DÂN TỘC TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -7322,7 +7322,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
+          <t>CÔNG TY CỔ PHẦN THUỶ ĐIỆN KÊNH BẮC - AYUN HẠ</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -7338,7 +7338,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -7354,7 +7354,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV XÂY DỰNG CÔNG THÀNH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LONG TRỌNG GIA LAI</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -7370,7 +7370,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
+          <t>CÔNG TY TNHH MTV XÂY DỰNG CÔNG THÀNH</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -7386,7 +7386,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LONG TRỌNG GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -7402,7 +7402,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THUỶ ĐIỆN KÊNH BẮC - AYUN HẠ</t>
+          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -7418,7 +7418,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -7450,7 +7450,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ATYCO</t>
+          <t>TRƯỜNG THCS KPA KLƠNG</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -7466,7 +7466,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS KPA KLƠNG</t>
+          <t>CÔNG TY TNHH ATYCO</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -7546,7 +7546,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CHANG FRUITS</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -7562,7 +7562,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
+          <t>CÔNG TY TNHH CHANG FRUITS</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -7674,7 +7674,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
+          <t>CÔNG TY BẢO MINH GIA LAI</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -7690,7 +7690,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO MINH GIA LAI</t>
+          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7738,7 +7738,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>ĐẢNG UỶ XÃ IA DÊR</t>
+          <t>HỘI KHUYẾN HỌC THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -7754,7 +7754,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>HỘI KHUYẾN HỌC THÀNH PHỐ PLEIKU</t>
+          <t>ĐẢNG UỶ XÃ IA DÊR</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -7978,7 +7978,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THANH NGÂN GIA LAI</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -8010,7 +8010,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
+          <t>CÔNG TY CP CHĂN NUÔI GIA LAI</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -8026,7 +8026,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CÔNG TY CP CHĂN NUÔI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -8042,7 +8042,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THANH NGÂN GIA LAI</t>
+          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -8234,7 +8234,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CÀ PHÊ 15</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG SƠN 145</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -8250,7 +8250,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG SƠN 145</t>
+          <t>PHÒNG AN NINH CHÍNH TRỊ NỘI BỘ - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -8266,7 +8266,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH CHÍNH TRỊ NỘI BỘ - CÔNG AN TỈNH GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CÀ PHÊ 15</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -8554,7 +8554,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU THẠCH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -8586,7 +8586,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU THẠCH GIA LAI</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -8634,7 +8634,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XÂY DỰNG THUỶ LỢI I</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN 732</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -8650,7 +8650,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN 732</t>
+          <t>CÔNG TY CỔ PHẦN XÂY DỰNG THUỶ LỢI I</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -8746,7 +8746,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẾ LÂM – TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -8778,7 +8778,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẾ LÂM – TÂY NGUYÊN</t>
+          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -8826,7 +8826,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -8842,7 +8842,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -8874,7 +8874,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -8954,7 +8954,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẬU CẦN 28 SANG AN GIA LAI</t>
+          <t>BAN QUẢN LÝ CHỢ HOA LƯ - PHÙ ĐỔNG</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -8970,7 +8970,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH Y DƯỢC ĐỨC HẠNH GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẬU CẦN 28 SANG AN GIA LAI</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -8986,7 +8986,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>UBND XÃ HÀ ĐÔNG</t>
+          <t>CÔNG TY TNHH Y DƯỢC ĐỨC HẠNH GIA LAI</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -9002,7 +9002,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ CHỢ HOA LƯ - PHÙ ĐỔNG</t>
+          <t>UBND XÃ HÀ ĐÔNG</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -9050,7 +9050,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>VNPT GIA LAI</t>
+          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -9114,7 +9114,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
+          <t>VNPT GIA LAI</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -9210,7 +9210,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>LIÊN ĐOÀN BÓNG ĐÁ VIỆT NAM</t>
+          <t>CHI NHÁNH CƠ KHÍ CÔNG TY CỔ PHẦN HOÀNG ANH GIA LAI</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -9226,7 +9226,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CƠ KHÍ CÔNG TY CỔ PHẦN HOÀNG ANH GIA LAI</t>
+          <t>LIÊN ĐOÀN BÓNG ĐÁ VIỆT NAM</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -9354,7 +9354,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÔNG ĐÀ 10.9</t>
+          <t>CÔNG TY TNHH NÔNG NGHIỆP NHÀ BÈ</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -9370,7 +9370,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NÔNG NGHIỆP NHÀ BÈ</t>
+          <t>CÔNG TY CỔ PHẦN SÔNG ĐÀ 10.9</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -9434,7 +9434,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN CHERR YBLOSSOM NHA TRANG TẠI GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN ANH KHOA MOTOR</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -9450,7 +9450,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN ANH KHOA MOTOR</t>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN CHERR YBLOSSOM NHA TRANG TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -9594,7 +9594,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU KIỂM</t>
+          <t>CÔNG TY CỔ PHẦN CHATHAM CIS</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -9610,7 +9610,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CHATHAM CIS</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU KIỂM</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -9642,7 +9642,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -9658,7 +9658,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -9770,7 +9770,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HỮU TÙNG GIA LAI</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -9786,7 +9786,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
+          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -9802,7 +9802,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HỮU TÙNG GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG PHẨM ATLANTIC VIỆT NAM</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -9818,7 +9818,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
+          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -9834,7 +9834,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG PHẨM ATLANTIC VIỆT NAM</t>
+          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -9946,7 +9946,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH RED RIVER FOODS VIỆT NAM TẠI GIA LAI</t>
+          <t>HỘI ĐỒNG NHÂN DÂN PHƯỜNG HỘI THƯƠNG</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -9962,7 +9962,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>HỘI ĐỒNG NHÂN DÂN PHƯỜNG HỘI THƯƠNG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH RED RIVER FOODS VIỆT NAM TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -9978,7 +9978,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>BẢO HIỂM XÃ HỘI TỈNH GIA LAI</t>
+          <t>TRUNG TÂM GIÁO DỤC THƯỜNG XUYÊN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -9994,7 +9994,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC THƯỜNG XUYÊN TỈNH GIA LAI</t>
+          <t>BẢO HIỂM XÃ HỘI TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -10058,7 +10058,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC SỐ 1 IA BĂNG</t>
+          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -10074,7 +10074,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
+          <t>CÔNG TY TNHH THT TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -10090,7 +10090,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THT TÂY NGUYÊN</t>
+          <t>TRƯỜNG TIỂU HỌC SỐ 1 IA BĂNG</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -10122,7 +10122,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
+          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -10138,7 +10138,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
+          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -10250,7 +10250,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
+          <t>HỒ ĐẮC TẤN</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -10266,7 +10266,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>HỒ ĐẮC TẤN</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -10410,7 +10410,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CÔNG AN THÀNH PHỐ PLEIKU</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẠNH NGUYÊN GIA LAI</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -10426,7 +10426,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẠNH NGUYÊN GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN BÓNG ĐÈN PHÍCH NƯỚC RẠNG ĐÔNG CHI NHÁNH TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -10442,7 +10442,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÓNG ĐÈN PHÍCH NƯỚC RẠNG ĐÔNG CHI NHÁNH TÂY NGUYÊN</t>
+          <t>CÔNG AN THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -10490,7 +10490,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>CÔNG TY CỔ PHẦN ĐỊNH GIÁ VÀ DỊCH VỤ TÀI CHÍNH HOÀNG CẦU</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -10522,7 +10522,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐỊNH GIÁ VÀ DỊCH VỤ TÀI CHÍNH HOÀNG CẦU</t>
+          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -10586,7 +10586,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SÔNG ĐÀ 4 - NHÀ MÁY THỦY ĐIỆN  IAGRAI  3</t>
+          <t>UỶ BAN NHÂN DÂN XÃ GÀO</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -10602,7 +10602,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ GÀO</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN SÔNG ĐÀ 4 - NHÀ MÁY THỦY ĐIỆN  IAGRAI  3</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -10650,7 +10650,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XỔ SỐ KIẾN THIẾT QUẢNG BÌNH</t>
+          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -10666,7 +10666,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XỔ SỐ KIẾN THIẾT QUẢNG BÌNH</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -10682,7 +10682,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
+          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -10746,7 +10746,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -10762,7 +10762,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -10858,7 +10858,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CỘNG ĐỒNG XE TẢI VIỆT NAM – CHI NHÁNH GIA LAI</t>
+          <t>TRUNG TÂM XỬ LÝ BOM MÌN VÀ MÔI TRƯỜNG</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -10874,7 +10874,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>TRUNG TÂM XỬ LÝ BOM MÌN VÀ MÔI TRƯỜNG</t>
+          <t>CÔNG TY CỔ PHẦN CỘNG ĐỒNG XE TẢI VIỆT NAM – CHI NHÁNH GIA LAI</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -11098,7 +11098,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>PA 05, CÔNG AN TỈNH GIA LAI</t>
+          <t>TRƯỜNG TIỂU HỌC SỐ 1 K'DANG</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -11114,7 +11114,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>CHI NHÁNH GIA LAI - TP.PLEIKU 3 - CÔNG TY CỔ PHẦN SAWAD TIỀN CÓ NGAY</t>
+          <t>TRƯỜNG THCS NGUYỄN VIẾT XUÂN</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -11146,7 +11146,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC SỐ 1 K'DANG</t>
+          <t>CHI NHÁNH GIA LAI - TP.PLEIKU 3 - CÔNG TY CỔ PHẦN SAWAD TIỀN CÓ NGAY</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -11162,7 +11162,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS NGUYỄN VIẾT XUÂN</t>
+          <t>PA 05, CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -11194,7 +11194,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
+          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -11226,7 +11226,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
+          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -11329,10 +11329,10 @@
         <v>0</v>
       </c>
       <c r="C682" t="n">
-        <v>13792149864</v>
+        <v>15592149878</v>
       </c>
       <c r="D682" t="n">
-        <v>-13792149864</v>
+        <v>-15592149878</v>
       </c>
     </row>
   </sheetData>
@@ -11346,7 +11346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11438,1392 +11438,1408 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ SAO NAM AN</t>
+          <t>ĐIỀU CHỈNH XNT</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>862895731</v>
+        <v>1482555255.000008</v>
       </c>
       <c r="D6" t="n">
-        <v>862895731</v>
+        <v>1482555255.000008</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐIỆN TỬ TIN HỌC KIM PHÁT</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ SAO NAM AN</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>721347450</v>
+        <v>862895731</v>
       </c>
       <c r="D7" t="n">
-        <v>721347450</v>
+        <v>862895731</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Công ty TNHH Phân phối Synnex FPT</t>
+          <t>CÔNG TY TNHH ĐIỆN TỬ TIN HỌC KIM PHÁT</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>610531458</v>
+        <v>721347450</v>
       </c>
       <c r="D8" t="n">
-        <v>610531458</v>
+        <v>721347450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NGÂN HÀNG TMCP Á CHÂU</t>
+          <t>Công ty TNHH Phân phối Synnex FPT</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>406726240</v>
+        <v>610531458</v>
       </c>
       <c r="D9" t="n">
-        <v>406726240</v>
+        <v>610531458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI PHƯƠNG VIỆT</t>
+          <t>NGÂN HÀNG TMCP Á CHÂU</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>309742718</v>
+        <v>406726240</v>
       </c>
       <c r="D10" t="n">
-        <v>309742718</v>
+        <v>406726240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MÁY TÍNH VĨNH XUÂN - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI PHƯƠNG VIỆT</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>302500001</v>
+        <v>309742718</v>
       </c>
       <c r="D11" t="n">
-        <v>302500001</v>
+        <v>309742718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XUẤT NHẬP KHẨU LÊ TRẦN GIA</t>
+          <t>CÔNG TY CỔ PHẦN MÁY TÍNH VĨNH XUÂN - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>289754543</v>
+        <v>302500001</v>
       </c>
       <c r="D12" t="n">
-        <v>289754543</v>
+        <v>302500001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC ANH PHƯƠNG A.P.C.O.M</t>
+          <t>CÔNG TY TNHH XUẤT NHẬP KHẨU LÊ TRẦN GIA</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>264727280</v>
+        <v>289754543</v>
       </c>
       <c r="D13" t="n">
-        <v>264727280</v>
+        <v>289754543</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MÁY TÍNH VĨNH XUÂN - CHI NHÁNH ĐÀ NẴNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC ANH PHƯƠNG A.P.C.O.M</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>246556363</v>
+        <v>264727280</v>
       </c>
       <c r="D14" t="n">
-        <v>246556363</v>
+        <v>264727280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN KỸ THUẬT CÔNG NGHỆ NAM THÀNH</t>
+          <t>CÔNG TY CỔ PHẦN MÁY TÍNH VĨNH XUÂN - CHI NHÁNH ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>214014544</v>
+        <v>246556363</v>
       </c>
       <c r="D15" t="n">
-        <v>214014544</v>
+        <v>246556363</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN HUETRONICS (TỈNH THỪA THIÊN HUẾ)</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN KỸ THUẬT CÔNG NGHỆ NAM THÀNH</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>213419911</v>
+        <v>214014544</v>
       </c>
       <c r="D16" t="n">
-        <v>213419911</v>
+        <v>214014544</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH CÔNG NGHỆ VÀ THƯƠNG MẠI Á MỸ</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN HUETRONICS (TỈNH THỪA THIÊN HUẾ)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>180123903</v>
+        <v>213419911</v>
       </c>
       <c r="D17" t="n">
-        <v>180123903</v>
+        <v>213419911</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ PHÁT TRIỂN CÔNG NGHỆ ROBO</t>
+          <t>CHI NHÁNH CÔNG TY TNHH CÔNG NGHỆ VÀ THƯƠNG MẠI Á MỸ</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>164390910</v>
+        <v>180123903</v>
       </c>
       <c r="D18" t="n">
-        <v>164390910</v>
+        <v>180123903</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHƯƠNG KHANG COMPUTER</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ PHÁT TRIỂN CÔNG NGHỆ ROBO</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>162469092</v>
+        <v>164390910</v>
       </c>
       <c r="D19" t="n">
-        <v>162469092</v>
+        <v>164390910</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chi nhánh Công ty TNHH phân phối Synnex FPT</t>
+          <t>CÔNG TY TNHH PHƯƠNG KHANG COMPUTER</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>161309081</v>
+        <v>162469092</v>
       </c>
       <c r="D20" t="n">
-        <v>161309081</v>
+        <v>162469092</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ &amp; THƯƠNG MẠI ĐẠI PHÁT</t>
+          <t>Chi nhánh Công ty TNHH phân phối Synnex FPT</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>126280000</v>
+        <v>161309081</v>
       </c>
       <c r="D21" t="n">
-        <v>126280000</v>
+        <v>161309081</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CÔNG NGHỆ DSS ĐÀ NẴNG</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ &amp; THƯƠNG MẠI ĐẠI PHÁT</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>114080012</v>
+        <v>126280000</v>
       </c>
       <c r="D22" t="n">
-        <v>114080012</v>
+        <v>126280000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT DIỆP KHÁNH</t>
+          <t>CÔNG TY TNHH CÔNG NGHỆ DSS ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>109546909</v>
+        <v>114080012</v>
       </c>
       <c r="D23" t="n">
-        <v>109546909</v>
+        <v>114080012</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN RIOTECH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT DIỆP KHÁNH</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>101218180</v>
+        <v>109546909</v>
       </c>
       <c r="D24" t="n">
-        <v>101218180</v>
+        <v>109546909</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MÁY TÍNH VĨNH XUÂN</t>
+          <t>CÔNG TY CỔ PHẦN RIOTECH</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>100599092</v>
+        <v>101218180</v>
       </c>
       <c r="D25" t="n">
-        <v>100599092</v>
+        <v>101218180</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIẢI PHÁP FINGERTAS</t>
+          <t>CÔNG TY CỔ PHẦN MÁY TÍNH VĨNH XUÂN</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>94350000</v>
+        <v>100599092</v>
       </c>
       <c r="D26" t="n">
-        <v>94350000</v>
+        <v>100599092</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Công ty TNHH Tin Học Kim Thiên Bảo</t>
+          <t>CÔNG TY TNHH GIẢI PHÁP FINGERTAS</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>91890911</v>
+        <v>94350000</v>
       </c>
       <c r="D27" t="n">
-        <v>91890911</v>
+        <v>94350000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
+          <t>Công ty TNHH Tin Học Kim Thiên Bảo</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>91625599</v>
+        <v>91890911</v>
       </c>
       <c r="D28" t="n">
-        <v>91625599</v>
+        <v>91890911</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ QUỐC VIỆT</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>88129073</v>
+        <v>91625599</v>
       </c>
       <c r="D29" t="n">
-        <v>88129073</v>
+        <v>91625599</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ CÔNG NGHỆ ÂM THANH TRIỆU GIA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ QUỐC VIỆT</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>87970000</v>
+        <v>88129073</v>
       </c>
       <c r="D30" t="n">
-        <v>87970000</v>
+        <v>88129073</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Công Nghệ Thông Tin An Phát</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ CÔNG NGHỆ ÂM THANH TRIỆU GIA</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>87445457</v>
+        <v>87970000</v>
       </c>
       <c r="D31" t="n">
-        <v>87445457</v>
+        <v>87970000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẢO NHIÊN</t>
+          <t>Công Ty TNHH Công Nghệ Thông Tin An Phát</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>82618181</v>
+        <v>87445457</v>
       </c>
       <c r="D32" t="n">
-        <v>82618181</v>
+        <v>87445457</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TIN HỌC VIẾT SƠN</t>
+          <t>CÔNG TY TNHH THẢO NHIÊN</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>79609101</v>
+        <v>82618181</v>
       </c>
       <c r="D33" t="n">
-        <v>79609101</v>
+        <v>82618181</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ LBM</t>
+          <t>CÔNG TY CỔ PHẦN TIN HỌC VIẾT SƠN</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>74545455</v>
+        <v>79609101</v>
       </c>
       <c r="D34" t="n">
-        <v>74545455</v>
+        <v>79609101</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH FINTECS</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ LBM</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>52581816</v>
+        <v>74545455</v>
       </c>
       <c r="D35" t="n">
-        <v>52581816</v>
+        <v>74545455</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN GIẢI PHÁP TIN HỌC ÁNH DƯƠNG</t>
+          <t>CÔNG TY TNHH FINTECS</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>52132000</v>
+        <v>52581816</v>
       </c>
       <c r="D36" t="n">
-        <v>52132000</v>
+        <v>52581816</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI CÔNG NGHỆ VÀ DỊCH VỤ MỚI RỒNG VIỆT</t>
+          <t>CÔNG TY CỔ PHẦN GIẢI PHÁP TIN HỌC ÁNH DƯƠNG</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>48481818</v>
+        <v>52132000</v>
       </c>
       <c r="D37" t="n">
-        <v>48481818</v>
+        <v>52132000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chi nhánh Công ty Cổ phần thương mại Tin học Hưng Long</t>
+          <t>CÔNG TY TNHH PHÂN PHỐI CÔNG NGHỆ VÀ DỊCH VỤ MỚI RỒNG VIỆT</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>46155808</v>
+        <v>48481818</v>
       </c>
       <c r="D38" t="n">
-        <v>46155808</v>
+        <v>48481818</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THIẾT BỊ VĂN PHÒNG NGUYỄN ĐỨC</t>
+          <t>Chi nhánh Công ty Cổ phần thương mại Tin học Hưng Long</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>45844275.91</v>
+        <v>46155808</v>
       </c>
       <c r="D39" t="n">
-        <v>45844275.91</v>
+        <v>46155808</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CÔNG NGHỆ TIN HỌC PHI LONG</t>
+          <t>CÔNG TY CỔ PHẦN THIẾT BỊ VĂN PHÒNG NGUYỄN ĐỨC</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>45272727</v>
+        <v>45844275.91</v>
       </c>
       <c r="D40" t="n">
-        <v>45272727</v>
+        <v>45844275.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI PHƯỚC THỌ</t>
+          <t>CÔNG TY TNHH CÔNG NGHỆ TIN HỌC PHI LONG</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>38148146.8</v>
+        <v>45272727</v>
       </c>
       <c r="D41" t="n">
-        <v>38148146.8</v>
+        <v>45272727</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Thương Mại LOGICO</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI PHƯỚC THỌ</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>33700000</v>
+        <v>38148146.8</v>
       </c>
       <c r="D42" t="n">
-        <v>33700000</v>
+        <v>38148146.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VPS MIỀN TRUNG</t>
+          <t>Công Ty TNHH Thương Mại LOGICO</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>30818182</v>
+        <v>33700000</v>
       </c>
       <c r="D43" t="n">
-        <v>30818182</v>
+        <v>33700000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG THÁI VIỆT ĐÀ NẴNG</t>
+          <t>CÔNG TY CỔ PHẦN VPS MIỀN TRUNG</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>30518183</v>
+        <v>30818182</v>
       </c>
       <c r="D44" t="n">
-        <v>30518183</v>
+        <v>30818182</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XUẤT NHẬP KHẨU KỸ NGHỆ Á ĐÔNG</t>
+          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG THÁI VIỆT ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>30181818</v>
+        <v>30518183</v>
       </c>
       <c r="D45" t="n">
-        <v>30181818</v>
+        <v>30518183</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+          <t>CÔNG TY CỔ PHẦN XUẤT NHẬP KHẨU KỸ NGHỆ Á ĐÔNG</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>26484916</v>
+        <v>30181818</v>
       </c>
       <c r="D46" t="n">
-        <v>26484916</v>
+        <v>30181818</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Một Thành Viên Bảo Vinh</t>
+          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>25363636</v>
+        <v>26484916</v>
       </c>
       <c r="D47" t="n">
-        <v>25363636</v>
+        <v>26484916</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH A.B.M</t>
+          <t>Công Ty TNHH Một Thành Viên Bảo Vinh</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>24300000</v>
+        <v>25363636</v>
       </c>
       <c r="D48" t="n">
-        <v>24300000</v>
+        <v>25363636</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ PHÁT TRIỂN CÔNG NGHỆ ĐỨC PHÁP</t>
+          <t>CÔNG TY TNHH A.B.M</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>21589965</v>
+        <v>24300000</v>
       </c>
       <c r="D49" t="n">
-        <v>21589965</v>
+        <v>24300000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI LONG CƯỜNG PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ PHÁT TRIỂN CÔNG NGHỆ ĐỨC PHÁP</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>21330000</v>
+        <v>21589965</v>
       </c>
       <c r="D50" t="n">
-        <v>21330000</v>
+        <v>21589965</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN PHAN QUANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI LONG CƯỜNG PHÁT</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>20181818</v>
+        <v>21330000</v>
       </c>
       <c r="D51" t="n">
-        <v>20181818</v>
+        <v>21330000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH ĐIỆN TỬ CÔNG NGHỆ TƯỜNG AN - T.A.K.O TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN PHAN QUANG</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>19756367</v>
+        <v>20181818</v>
       </c>
       <c r="D52" t="n">
-        <v>19756367</v>
+        <v>20181818</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI CÔNG NGHỆ ĐẠI TÀI LỘC</t>
+          <t>CHI NHÁNH CÔNG TY TNHH ĐIỆN TỬ CÔNG NGHỆ TƯỜNG AN - T.A.K.O TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>18727273</v>
+        <v>19756367</v>
       </c>
       <c r="D53" t="n">
-        <v>18727273</v>
+        <v>19756367</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DỊCH VỤ THƯƠNG MẠI MẠNH TÀI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI CÔNG NGHỆ ĐẠI TÀI LỘC</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>17045454</v>
+        <v>18727273</v>
       </c>
       <c r="D54" t="n">
-        <v>17045454</v>
+        <v>18727273</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ SẢN XUẤT XUẤT NHẬP KHẨU MỰC IN VIỆT NHẬT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DỊCH VỤ THƯƠNG MẠI MẠNH TÀI</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>15615058</v>
+        <v>17045454</v>
       </c>
       <c r="D55" t="n">
-        <v>15615058</v>
+        <v>17045454</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ SẢN XUẤT XUẤT NHẬP KHẨU MỰC IN VIỆT NHẬT</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>14699277</v>
+        <v>15615058</v>
       </c>
       <c r="D56" t="n">
-        <v>14699277</v>
+        <v>15615058</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VI TÍNH NGUYÊN KIM</t>
+          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>13527272</v>
+        <v>14699277</v>
       </c>
       <c r="D57" t="n">
-        <v>13527272</v>
+        <v>14699277</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MÁY TÍNH KIẾN HÒA</t>
+          <t>CÔNG TY TNHH VI TÍNH NGUYÊN KIM</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>13363636</v>
+        <v>13527272</v>
       </c>
       <c r="D58" t="n">
-        <v>13363636</v>
+        <v>13527272</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG THƯƠNG MẠI VÀ TƯ VẤN TRÍ VIỄN</t>
+          <t>CÔNG TY TNHH MÁY TÍNH KIẾN HÒA</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>13362727</v>
+        <v>13363636</v>
       </c>
       <c r="D59" t="n">
-        <v>13362727</v>
+        <v>13363636</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CÔNG NGHỆ TIN HỌC TG</t>
+          <t>CÔNG TY TNHH XÂY DỰNG THƯƠNG MẠI VÀ TƯ VẤN TRÍ VIỄN</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>12727273</v>
+        <v>13362727</v>
       </c>
       <c r="D60" t="n">
-        <v>12727273</v>
+        <v>13362727</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH THƯƠNG MẠI - ĐẦU TƯ VÀ PHÁT TRIỂN</t>
+          <t>CÔNG TY TNHH CÔNG NGHỆ TIN HỌC TG</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>9862000</v>
+        <v>12727273</v>
       </c>
       <c r="D61" t="n">
-        <v>9862000</v>
+        <v>12727273</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PHÂN PHỐI ĐIỆN TỬ JVS</t>
+          <t>CHI NHÁNH CÔNG TY TNHH THƯƠNG MẠI - ĐẦU TƯ VÀ PHÁT TRIỂN</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>9680000</v>
+        <v>9862000</v>
       </c>
       <c r="D62" t="n">
-        <v>9680000</v>
+        <v>9862000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ MÁY VĂN PHÒNG MINH PHỤNG</t>
+          <t>CÔNG TY CỔ PHẦN PHÂN PHỐI ĐIỆN TỬ JVS</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>9227271.890000001</v>
+        <v>9680000</v>
       </c>
       <c r="D63" t="n">
-        <v>9227271.890000001</v>
+        <v>9680000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ALOHA VINA</t>
+          <t>CÔNG TY TNHH DỊCH VỤ MÁY VĂN PHÒNG MINH PHỤNG</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>8134545</v>
+        <v>9227271.890000001</v>
       </c>
       <c r="D64" t="n">
-        <v>8134545</v>
+        <v>9227271.890000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Công Nghệ Và Thương Mại Mai Khanh</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ALOHA VINA</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>8042595</v>
+        <v>8134545</v>
       </c>
       <c r="D65" t="n">
-        <v>8042595</v>
+        <v>8134545</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PHÂN PHỐI TÂN NIỀM TIN</t>
+          <t>Công Ty TNHH Công Nghệ Và Thương Mại Mai Khanh</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>7886370</v>
+        <v>8042595</v>
       </c>
       <c r="D66" t="n">
-        <v>7886370</v>
+        <v>8042595</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VĨNH TÍN</t>
+          <t>CÔNG TY CỔ PHẦN PHÂN PHỐI TÂN NIỀM TIN</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>7418182</v>
+        <v>7886370</v>
       </c>
       <c r="D67" t="n">
-        <v>7418182</v>
+        <v>7886370</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VIỄN THÔNG HOÀN PHÁT</t>
+          <t>CÔNG TY TNHH VĨNH TÍN</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>7045457</v>
+        <v>7418182</v>
       </c>
       <c r="D68" t="n">
-        <v>7045457</v>
+        <v>7418182</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV XĂNG DẦU BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH VIỄN THÔNG HOÀN PHÁT</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>6091306</v>
+        <v>7045457</v>
       </c>
       <c r="D69" t="n">
-        <v>6091306</v>
+        <v>7045457</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CÔNG NGHỆ ÂU LẠC</t>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>5413637</v>
+        <v>6091306</v>
       </c>
       <c r="D70" t="n">
-        <v>5413637</v>
+        <v>6091306</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY TNHH CÔNG NGHỆ ÂU LẠC</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>4628168</v>
+        <v>5413637</v>
       </c>
       <c r="D71" t="n">
-        <v>4628168</v>
+        <v>5413637</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TIN HỌC QUỐC PHƯƠNG</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>4316818.18</v>
+        <v>4628168</v>
       </c>
       <c r="D72" t="n">
-        <v>4316818.18</v>
+        <v>4628168</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TIN HỌC QUỐC PHƯƠNG</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>4000000</v>
+        <v>4316818.18</v>
       </c>
       <c r="D73" t="n">
-        <v>4000000</v>
+        <v>4316818.18</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KỸ THUẬT CÔNG NGHỆ HẢI SƠN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
       <c r="D74" t="n">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TP-LINK TECHNOLOGIES VIỆT NAM</t>
+          <t>CÔNG TY TNHH KỸ THUẬT CÔNG NGHỆ HẢI SƠN</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>3255452</v>
+        <v>3900000</v>
       </c>
       <c r="D75" t="n">
-        <v>3255452</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t>CÔNG TY TNHH TP-LINK TECHNOLOGIES VIỆT NAM</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>3142498</v>
+        <v>3255452</v>
       </c>
       <c r="D76" t="n">
-        <v>3142498</v>
+        <v>3255452</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Công ty TNHH TP-Link Technologies Việt Nam</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>2798181</v>
+        <v>3142498</v>
       </c>
       <c r="D77" t="n">
-        <v>2798181</v>
+        <v>3142498</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM DV XNK PHẠM GIA KHANG</t>
+          <t>Công ty TNHH TP-Link Technologies Việt Nam</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>2727273</v>
+        <v>2798181</v>
       </c>
       <c r="D78" t="n">
-        <v>2727273</v>
+        <v>2798181</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM DV XNK PHẠM GIA KHANG</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>1774500</v>
+        <v>2727273</v>
       </c>
       <c r="D79" t="n">
-        <v>1774500</v>
+        <v>2727273</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI &amp; DỊCH VỤ ĐẠI SƠN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>1613636</v>
+        <v>1774500</v>
       </c>
       <c r="D80" t="n">
-        <v>1613636</v>
+        <v>1774500</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN GIẢI PHÁP MẠNG VÀ MÁY TÍNH TIC</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI &amp; DỊCH VỤ ĐẠI SƠN</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>1500000</v>
+        <v>1613636</v>
       </c>
       <c r="D81" t="n">
-        <v>1500000</v>
+        <v>1613636</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Mắt Bão</t>
+          <t>CÔNG TY CỔ PHẦN GIẢI PHÁP MẠNG VÀ MÁY TÍNH TIC</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>1188000</v>
+        <v>1500000</v>
       </c>
       <c r="D82" t="n">
-        <v>1188000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
+          <t>Công ty Cổ phần Mắt Bão</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>1041711</v>
+        <v>1188000</v>
       </c>
       <c r="D83" t="n">
-        <v>1041711</v>
+        <v>1188000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CÔNG NGHỆ VI MÔ</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>957428</v>
+        <v>1041711</v>
       </c>
       <c r="D84" t="n">
-        <v>957428</v>
+        <v>1041711</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP PHAT TRIEN THANH PHO HO CHI MINH</t>
+          <t>CÔNG TY CỔ PHẦN CÔNG NGHỆ VI MÔ</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>697428</v>
+        <v>957428</v>
       </c>
       <c r="D85" t="n">
-        <v>697428</v>
+        <v>957428</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TM DV VĂN PHÒNG PHẨM SƠN THỦY</t>
+          <t>NGAN HANG TMCP PHAT TRIEN THANH PHO HO CHI MINH</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>590000</v>
+        <v>697428</v>
       </c>
       <c r="D86" t="n">
-        <v>590000</v>
+        <v>697428</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI DỊCH VỤ TỔNG HỢP XUÂN TÙNG</t>
+          <t>CÔNG TY TNHH TM DV VĂN PHÒNG PHẨM SƠN THỦY</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>490909</v>
+        <v>590000</v>
       </c>
       <c r="D87" t="n">
-        <v>490909</v>
+        <v>590000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI DỊCH VỤ TỔNG HỢP XUÂN TÙNG</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>403367</v>
+        <v>490909</v>
       </c>
       <c r="D88" t="n">
-        <v>403367</v>
+        <v>490909</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ THƯƠNG MẠI PHÁT TRIỂN NHẤT TÍN</t>
+          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>238704</v>
+        <v>403367</v>
       </c>
       <c r="D89" t="n">
-        <v>238704</v>
+        <v>403367</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN T.K TECHNOLOGY GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ THƯƠNG MẠI PHÁT TRIỂN NHẤT TÍN</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>163636</v>
+        <v>238704</v>
       </c>
       <c r="D90" t="n">
-        <v>163636</v>
+        <v>238704</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN T.K TECHNOLOGY GIA LAI</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>77000</v>
+        <v>163636</v>
       </c>
       <c r="D91" t="n">
-        <v>77000</v>
+        <v>163636</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>77000</v>
+      </c>
+      <c r="D92" t="n">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN AN BÌNH - CHI NHÁNH GIA LAI</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="n">
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="n">
         <v>2000</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D93" t="n">
         <v>2000</v>
       </c>
     </row>

--- a/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
+++ b/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
@@ -3322,7 +3322,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TRƯỜNG TRUNG HỌC CƠ SỞ NGÔ GIA TỰ</t>
+          <t>BAN QUẢN LÝ DỰ ÁN - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3338,7 +3338,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ DỰ ÁN - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>TRƯỜNG TRUNG HỌC CƠ SỞ NGÔ GIA TỰ</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3546,7 +3546,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG GIA HUY - GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3578,7 +3578,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG GIA HUY - GIA LAI</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3674,7 +3674,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THIẾT KẾ XÂY DỰNG KIẾN XANH GIA LAI</t>
+          <t>CÔNG TY TNHH KẾ TOÁN SANG VY GIA LAI</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3690,7 +3690,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KẾ TOÁN SANG VY GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THIẾT KẾ XÂY DỰNG KIẾN XANH GIA LAI</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3962,7 +3962,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG THƯƠNG MẠI VÀ DỊCH VỤ AN PHÚ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DƯỢC PHẨM PHÚ VINH GIA LAI</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3978,7 +3978,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DƯỢC PHẨM PHÚ VINH GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG THƯƠNG MẠI VÀ DỊCH VỤ AN PHÚ</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4042,7 +4042,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TÍN THÀNH ĐẠT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC HOÀNG KIM PHÁT</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -4058,7 +4058,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC HOÀNG KIM PHÁT</t>
+          <t>CÔNG TY CỔ PHẦN TÍN THÀNH ĐẠT</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -4218,7 +4218,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NHÔM KÍNH HÀ TIÊN GL</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ PVOIL MIỀN TRUNG TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -4234,7 +4234,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ PVOIL MIỀN TRUNG TẠI GIA LAI</t>
+          <t>CÔNG TY TNHH NHÔM KÍNH HÀ TIÊN GL</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5818,7 +5818,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP - GIÁO DỤC THƯỜNG XUYÊN HUYỆN CHƯ PĂH</t>
+          <t>Tiểu Đoàn Bộ Binh 50</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -5834,7 +5834,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Tiểu Đoàn Bộ Binh 50</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP - GIÁO DỤC THƯỜNG XUYÊN HUYỆN CHƯ PĂH</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -6090,7 +6090,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Phòng Chính Trị, Bộ Tham Mưu, Quân Đoàn 3</t>
+          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐỨC CƠ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -6106,7 +6106,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐỨC CƠ</t>
+          <t>Phòng Chính Trị, Bộ Tham Mưu, Quân Đoàn 3</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -6154,7 +6154,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC LÊ HỒNG PHONG</t>
+          <t>TRUNG ĐOÀN BỘ BINH 991</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -6170,7 +6170,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>TRUNG ĐOÀN BỘ BINH 991</t>
+          <t>TRƯỜNG TIỂU HỌC LÊ HỒNG PHONG</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -6234,7 +6234,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>LIÊN MINH HỢP TÁC XÃ TỈNH GIA LAI</t>
+          <t>CÔNG TY TNHH KIM GIA HUY GL</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -6250,7 +6250,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM GIA HUY GL</t>
+          <t>LIÊN MINH HỢP TÁC XÃ TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -6538,7 +6538,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI HÀ TIÊN GIA LAI</t>
+          <t>CÔNG TY TNHH PHÁT TRIỂN CÔNG NGHỆ VIDANA</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -6554,7 +6554,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÁT TRIỂN CÔNG NGHỆ VIDANA</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI HÀ TIÊN GIA LAI</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -7002,7 +7002,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
+          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -7018,7 +7018,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ VPS</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -7034,7 +7034,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ VPS</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -7050,7 +7050,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
+          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -7338,7 +7338,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LONG TRỌNG GIA LAI</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -7354,7 +7354,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LONG TRỌNG GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -7386,7 +7386,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
+          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -7402,7 +7402,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -7418,7 +7418,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -7546,7 +7546,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
+          <t>CÔNG TY TNHH CHANG FRUITS</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -7562,7 +7562,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CHANG FRUITS</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -7674,7 +7674,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO MINH GIA LAI</t>
+          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -7690,7 +7690,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
+          <t>CÔNG TY BẢO MINH GIA LAI</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7978,7 +7978,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THANH NGÂN GIA LAI</t>
+          <t>TRƯỜNG THCS TRẦN PHÚ</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -7994,7 +7994,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS TRẦN PHÚ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -8026,7 +8026,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
+          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -8042,7 +8042,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THANH NGÂN GIA LAI</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -8554,7 +8554,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU THẠCH GIA LAI</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -8570,7 +8570,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐIỆN GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -8586,7 +8586,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU THẠCH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN ĐIỆN GIA LAI</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -8746,7 +8746,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẾ LÂM – TÂY NGUYÊN</t>
+          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -8762,7 +8762,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>TRUNG TÂM VĂN HÓA, THÔNG TIN VÀ THỂ THAO THÀNH PHỐ PLEIKU</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẾ LÂM – TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -8778,7 +8778,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
+          <t>TRUNG TÂM VĂN HÓA, THÔNG TIN VÀ THỂ THAO THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -8826,7 +8826,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -8842,7 +8842,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -8874,7 +8874,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -8970,7 +8970,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẬU CẦN 28 SANG AN GIA LAI</t>
+          <t>CÔNG TY TNHH Y DƯỢC ĐỨC HẠNH GIA LAI</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -8986,7 +8986,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH Y DƯỢC ĐỨC HẠNH GIA LAI</t>
+          <t>UBND XÃ HÀ ĐÔNG</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -9002,7 +9002,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>UBND XÃ HÀ ĐÔNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẬU CẦN 28 SANG AN GIA LAI</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -9018,7 +9018,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG NAM ANH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN TIẾN NÔNG GIA LAI</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -9034,7 +9034,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TIẾN NÔNG GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG NAM ANH GIA LAI</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -9050,7 +9050,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
+          <t>CÔNG TY TNHH BÁCH CÁT NGUYÊN</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -9066,7 +9066,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BÁCH CÁT NGUYÊN</t>
+          <t>VNPT GIA LAI</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -9082,7 +9082,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MẠNH THẮNG GLC</t>
+          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -9098,7 +9098,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>CÔNG TY TRUYỀN TẢI ĐIỆN 3</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MẠNH THẮNG GLC</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -9114,7 +9114,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>VNPT GIA LAI</t>
+          <t>CÔNG TY TRUYỀN TẢI ĐIỆN 3</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -9210,7 +9210,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CƠ KHÍ CÔNG TY CỔ PHẦN HOÀNG ANH GIA LAI</t>
+          <t>LIÊN ĐOÀN BÓNG ĐÁ VIỆT NAM</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -9226,7 +9226,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>LIÊN ĐOÀN BÓNG ĐÁ VIỆT NAM</t>
+          <t>KHO K896/CQK</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -9242,7 +9242,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>KHO K896/CQK</t>
+          <t>CHI NHÁNH CƠ KHÍ CÔNG TY CỔ PHẦN HOÀNG ANH GIA LAI</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -9322,7 +9322,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG TUẤN TÚ GIA LAI</t>
+          <t>CỬA HÀNG CÔNG NGHỆ KHOA HỌC KỸ THUẬT PHAN ANH</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -9338,7 +9338,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>CỬA HÀNG CÔNG NGHỆ KHOA HỌC KỸ THUẬT PHAN ANH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG TUẤN TÚ GIA LAI</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -9354,7 +9354,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NÔNG NGHIỆP NHÀ BÈ</t>
+          <t>CÔNG TY CỔ PHẦN SÔNG ĐÀ 10.9</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -9370,7 +9370,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÔNG ĐÀ 10.9</t>
+          <t>CÔNG TY TNHH NÔNG NGHIỆP NHÀ BÈ</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -9562,7 +9562,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẦM NON THỊ TRẤN IALY</t>
+          <t>PHÒNG QUẢN LÝ ĐÔ THỊ THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -9578,7 +9578,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>PHÒNG QUẢN LÝ ĐÔ THỊ THÀNH PHỐ PLEIKU</t>
+          <t>TRƯỜNG MẦM NON THỊ TRẤN IALY</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -9642,7 +9642,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -9658,7 +9658,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -9786,7 +9786,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
+          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -9818,7 +9818,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
+          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -9834,7 +9834,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
+          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -9866,7 +9866,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC SÊ</t>
+          <t>CỤM 2287 - BTM - QUÂN KHU 5</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -9882,7 +9882,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CỤM 2287 - BTM - QUÂN KHU 5</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC SÊ</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -9946,7 +9946,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>HỘI ĐỒNG NHÂN DÂN PHƯỜNG HỘI THƯƠNG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH RED RIVER FOODS VIỆT NAM TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -9962,7 +9962,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH RED RIVER FOODS VIỆT NAM TẠI GIA LAI</t>
+          <t>HỘI ĐỒNG NHÂN DÂN PHƯỜNG HỘI THƯƠNG</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -10058,7 +10058,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
+          <t>CÔNG TY TNHH THT TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -10074,7 +10074,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THT TÂY NGUYÊN</t>
+          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -10122,7 +10122,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
+          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -10138,7 +10138,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
+          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -10266,7 +10266,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
+          <t>UBND XÃ IA BĂNG</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -10282,7 +10282,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>UBND XÃ IA BĂNG</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -10410,7 +10410,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẠNH NGUYÊN GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN BÓNG ĐÈN PHÍCH NƯỚC RẠNG ĐÔNG CHI NHÁNH TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -10426,7 +10426,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÓNG ĐÈN PHÍCH NƯỚC RẠNG ĐÔNG CHI NHÁNH TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẠNH NGUYÊN GIA LAI</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -10490,7 +10490,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐỊNH GIÁ VÀ DỊCH VỤ TÀI CHÍNH HOÀNG CẦU</t>
+          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -10522,7 +10522,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>CÔNG TY CỔ PHẦN ĐỊNH GIÁ VÀ DỊCH VỤ TÀI CHÍNH HOÀNG CẦU</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -10570,7 +10570,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ CHUYÊN NGHIỆP HÂN NAM</t>
+          <t>UỶ BAN NHÂN DÂN XÃ GÀO</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -10586,7 +10586,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ GÀO</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ CHUYÊN NGHIỆP HÂN NAM</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -10650,7 +10650,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XỔ SỐ KIẾN THIẾT QUẢNG BÌNH</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -10666,7 +10666,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XỔ SỐ KIẾN THIẾT QUẢNG BÌNH</t>
+          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -10682,7 +10682,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
+          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -10746,7 +10746,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -10762,7 +10762,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -10810,7 +10810,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI &amp; DỊCH VỤ ĐÔNG HUY</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -10826,7 +10826,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI &amp; DỊCH VỤ ĐÔNG HUY</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -10858,7 +10858,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>TRUNG TÂM XỬ LÝ BOM MÌN VÀ MÔI TRƯỜNG</t>
+          <t>CÔNG TY CỔ PHẦN CỘNG ĐỒNG XE TẢI VIỆT NAM – CHI NHÁNH GIA LAI</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -10874,7 +10874,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CỘNG ĐỒNG XE TẢI VIỆT NAM – CHI NHÁNH GIA LAI</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY THƯƠNG MẠI KỸ THUẬT VÀ ĐẦU TƯ - CÔNG TY CỔ PHẦN TẠI TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -10890,7 +10890,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY THƯƠNG MẠI KỸ THUẬT VÀ ĐẦU TƯ - CÔNG TY CỔ PHẦN TẠI TỈNH GIA LAI</t>
+          <t>TRUNG TÂM XỬ LÝ BOM MÌN VÀ MÔI TRƯỜNG</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -11018,7 +11018,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ Y KHOA TÂM AN</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ AN NINH ĐẤT VIỆT</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -11034,7 +11034,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ AN NINH ĐẤT VIỆT</t>
+          <t>CÔNG TY TNHH THIẾT BỊ Y KHOA TÂM AN</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -11066,7 +11066,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CHẾ BIẾN THỨC ĂN GIA SÚC ĐÔNG GIA LAI</t>
+          <t>CÔNG TY TNHH CHẤT LƯỢNG GIA LAI</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -11082,7 +11082,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CHẤT LƯỢNG GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN CHẾ BIẾN THỨC ĂN GIA SÚC ĐÔNG GIA LAI</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -11098,7 +11098,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC SỐ 1 K'DANG</t>
+          <t>VĂN PHÒNG LUẬT SƯ HỨA HOÀNG GIA</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -11114,7 +11114,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS NGUYỄN VIẾT XUÂN</t>
+          <t>PA 05, CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -11130,7 +11130,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG LUẬT SƯ HỨA HOÀNG GIA</t>
+          <t>TRƯỜNG TIỂU HỌC SỐ 1 K'DANG</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -11162,7 +11162,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>PA 05, CÔNG AN TỈNH GIA LAI</t>
+          <t>TRƯỜNG THCS NGUYỄN VIẾT XUÂN</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -11194,7 +11194,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
+          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -11210,7 +11210,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ GIAO HÀNG NHANH</t>
+          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -11226,7 +11226,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ GIAO HÀNG NHANH</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -11445,10 +11445,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1482555255.000008</v>
+        <v>1484670070.000008</v>
       </c>
       <c r="D6" t="n">
-        <v>1482555255.000008</v>
+        <v>1484670070.000008</v>
       </c>
     </row>
     <row r="7">

--- a/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
+++ b/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
@@ -3322,7 +3322,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ DỰ ÁN - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>TRƯỜNG TRUNG HỌC CƠ SỞ NGÔ GIA TỰ</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3338,7 +3338,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TRƯỜNG TRUNG HỌC CƠ SỞ NGÔ GIA TỰ</t>
+          <t>BAN QUẢN LÝ DỰ ÁN - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3546,7 +3546,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẠT LINH GIA LAI</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3562,7 +3562,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TƯ VẤN VÀ XÂY DỰNG DQT</t>
+          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3578,7 +3578,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG GIA HUY - GIA LAI</t>
+          <t>CÔNG TY TNHH TƯ VẤN VÀ XÂY DỰNG DQT</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3594,7 +3594,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẠT LINH GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG GIA HUY - GIA LAI</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3770,7 +3770,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ ĐĂK RING</t>
+          <t>CHI CỤC THI HÀNH ÁN DÂN SỰ HUYỆN ĐAK ĐOA</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -3786,7 +3786,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CHI CỤC THI HÀNH ÁN DÂN SỰ HUYỆN ĐAK ĐOA</t>
+          <t>TRƯỜNG MẦM NON TRÀ MY</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3802,7 +3802,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẦM NON TRÀ MY</t>
+          <t>UỶ BAN NHÂN DÂN XÃ ĐĂK RING</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3962,7 +3962,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DƯỢC PHẨM PHÚ VINH GIA LAI</t>
+          <t>UỶ BAN NHÂN DÂN XÃ KON GANG</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3994,7 +3994,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ KON GANG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DƯỢC PHẨM PHÚ VINH GIA LAI</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5098,7 +5098,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HỒNG SINH PHÁT GIA LAI</t>
+          <t>QUỸ HỖ TRỢ PHÁT TRIỂN HỢP TÁC XÃ TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -5114,7 +5114,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>QUỸ HỖ TRỢ PHÁT TRIỂN HỢP TÁC XÃ TỈNH GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HỒNG SINH PHÁT GIA LAI</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -5162,7 +5162,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XÂY DỰNG 711</t>
+          <t>TRƯỜNG MẪU GIÁO SAO MAI</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -5178,7 +5178,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẪU GIÁO SAO MAI</t>
+          <t>CÔNG TY CỔ PHẦN XÂY DỰNG 711</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -5530,7 +5530,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Trại giống cây trồng - Binh đoàn 16</t>
+          <t>LÊ THỊ LINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -5546,7 +5546,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>LÊ THỊ LINH PHƯƠNG</t>
+          <t>Trại giống cây trồng - Binh đoàn 16</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -5594,7 +5594,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CẢNH QUANG GIA LAI</t>
+          <t>TRƯỜNG THPT NGUYỄN THỊ MINH KHAI</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -5610,7 +5610,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>TRƯỜNG THPT NGUYỄN THỊ MINH KHAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CẢNH QUANG GIA LAI</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -5834,7 +5834,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP - GIÁO DỤC THƯỜNG XUYÊN HUYỆN CHƯ PĂH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KIẾN TRÚC XÂY DỰNG TDH</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -5850,7 +5850,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KIẾN TRÚC XÂY DỰNG TDH</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP - GIÁO DỤC THƯỜNG XUYÊN HUYỆN CHƯ PĂH</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -6026,7 +6026,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HUẤN LUYỆN VÀ THI ĐẤU THỂ THAO TÍNH</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGON AVATAR - NHÀ HÀNG NGON 3 MIỀN</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -6042,7 +6042,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGON AVATAR - NHÀ HÀNG NGON 3 MIỀN</t>
+          <t>TRUNG TÂM HUẤN LUYỆN VÀ THI ĐẤU THỂ THAO TÍNH</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -6090,7 +6090,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐỨC CƠ</t>
+          <t>Phòng Chính Trị, Bộ Tham Mưu, Quân Đoàn 3</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -6106,7 +6106,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Phòng Chính Trị, Bộ Tham Mưu, Quân Đoàn 3</t>
+          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐỨC CƠ</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -6138,7 +6138,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP -GIÁO DỤC THƯỜNG XUYÊN HUYỆN ĐAK ĐOA</t>
+          <t>TRƯỜNG TIỂU HỌC LÊ HỒNG PHONG</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -6170,7 +6170,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC LÊ HỒNG PHONG</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP -GIÁO DỤC THƯỜNG XUYÊN HUYỆN ĐAK ĐOA</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -6506,7 +6506,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>HOÀNG THỊ HỒNG MINH - CỬA HÀNG THƯƠNG MẠI VÀ DỊCH VỤ THIẾT BỊ VĂN PHÒNG MINH PHÁT</t>
+          <t>CÔNG TY TNHH HG AGRI</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -6522,7 +6522,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HG AGRI</t>
+          <t>HOÀNG THỊ HỒNG MINH - CỬA HÀNG THƯƠNG MẠI VÀ DỊCH VỤ THIẾT BỊ VĂN PHÒNG MINH PHÁT</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -7002,7 +7002,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
+          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -7018,7 +7018,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ VPS</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -7034,7 +7034,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ VPS</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -7050,7 +7050,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
+          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -7114,7 +7114,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOÀNG AUTO GIA LAI</t>
+          <t>CÔNG TY TNHH ANDRITZ VIỆT NAM</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -7130,7 +7130,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>UBND XÃ IA TÔ</t>
+          <t>CÔNG TY TNHH HOÀNG AUTO GIA LAI</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -7146,7 +7146,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ANDRITZ VIỆT NAM</t>
+          <t>UBND XÃ IA TÔ</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -7226,7 +7226,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Đồn Biên phòng Ia Lốp</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THẨM ĐỊNH GIÁ VINACONTROL - TẠI ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -7242,7 +7242,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THẨM ĐỊNH GIÁ VINACONTROL - TẠI ĐÀ NẴNG</t>
+          <t>Đồn Biên phòng Ia Lốp</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -7322,7 +7322,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THUỶ ĐIỆN KÊNH BẮC - AYUN HẠ</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -7338,7 +7338,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LONG TRỌNG GIA LAI</t>
+          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -7354,7 +7354,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN THUỶ ĐIỆN KÊNH BẮC - AYUN HẠ</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -7370,7 +7370,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV XÂY DỰNG CÔNG THÀNH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -7386,7 +7386,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -7402,7 +7402,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LONG TRỌNG GIA LAI</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -7418,7 +7418,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
+          <t>CÔNG TY TNHH MTV XÂY DỰNG CÔNG THÀNH</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -7450,7 +7450,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS KPA KLƠNG</t>
+          <t>CÔNG TY TNHH ATYCO</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -7466,7 +7466,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ATYCO</t>
+          <t>TRƯỜNG THCS KPA KLƠNG</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -7546,7 +7546,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH CHANG FRUITS</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -7562,7 +7562,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
+          <t>CÔNG TY TNHH CHANG FRUITS</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -7674,7 +7674,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
+          <t>CÔNG TY BẢO MINH GIA LAI</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -7690,7 +7690,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO MINH GIA LAI</t>
+          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7738,7 +7738,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>HỘI KHUYẾN HỌC THÀNH PHỐ PLEIKU</t>
+          <t>ĐẢNG UỶ XÃ IA DÊR</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -7754,7 +7754,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>ĐẢNG UỶ XÃ IA DÊR</t>
+          <t>HỘI KHUYẾN HỌC THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -7898,7 +7898,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ XÂY DỰNG TRƯỜNG THỊNH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CÀ PHÊ THU HƯỜNG</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -7914,7 +7914,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CÀ PHÊ THU HƯỜNG</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ XÂY DỰNG TRƯỜNG THỊNH</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -7978,7 +7978,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS TRẦN PHÚ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THANH NGÂN GIA LAI</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -7994,7 +7994,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
+          <t>CÔNG TY CP CHĂN NUÔI GIA LAI</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -8010,7 +8010,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CÔNG TY CP CHĂN NUÔI GIA LAI</t>
+          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -8026,7 +8026,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
+          <t>TRƯỜNG THCS TRẦN PHÚ</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -8042,7 +8042,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THANH NGÂN GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -8122,7 +8122,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẦM NON SAO KHUÊ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BROTHER INTERNATIONAL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -8138,7 +8138,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BROTHER INTERNATIONAL (VIỆT NAM)</t>
+          <t>TRƯỜNG MẦM NON SAO KHUÊ</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -8234,7 +8234,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG SƠN 145</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CÀ PHÊ 15</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -8250,7 +8250,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH CHÍNH TRỊ NỘI BỘ - CÔNG AN TỈNH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG SƠN 145</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -8266,7 +8266,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CÀ PHÊ 15</t>
+          <t>PHÒNG AN NINH CHÍNH TRỊ NỘI BỘ - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -8554,7 +8554,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU THẠCH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -8570,7 +8570,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU THẠCH GIA LAI</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -8746,7 +8746,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẾ LÂM – TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -8762,7 +8762,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẾ LÂM – TÂY NGUYÊN</t>
+          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -8826,7 +8826,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -8842,7 +8842,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
+          <t>CÔNG TY TNHH DỊCH VỤ NÔNG NGHIỆP TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -8858,7 +8858,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ NÔNG NGHIỆP TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -8874,7 +8874,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -9018,7 +9018,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TIẾN NÔNG GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG NAM ANH GIA LAI</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -9034,7 +9034,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG NAM ANH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN TIẾN NÔNG GIA LAI</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -9050,7 +9050,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BÁCH CÁT NGUYÊN</t>
+          <t>CÔNG TY TRUYỀN TẢI ĐIỆN 3</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -9066,7 +9066,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>VNPT GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MẠNH THẮNG GLC</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -9082,7 +9082,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
+          <t>VNPT GIA LAI</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -9098,7 +9098,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MẠNH THẮNG GLC</t>
+          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -9114,7 +9114,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CÔNG TY TRUYỀN TẢI ĐIỆN 3</t>
+          <t>CÔNG TY TNHH BÁCH CÁT NGUYÊN</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -9226,7 +9226,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>KHO K896/CQK</t>
+          <t>CHI NHÁNH CƠ KHÍ CÔNG TY CỔ PHẦN HOÀNG ANH GIA LAI</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -9242,7 +9242,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CƠ KHÍ CÔNG TY CỔ PHẦN HOÀNG ANH GIA LAI</t>
+          <t>KHO K896/CQK</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -9322,7 +9322,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>CỬA HÀNG CÔNG NGHỆ KHOA HỌC KỸ THUẬT PHAN ANH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG TUẤN TÚ GIA LAI</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -9338,7 +9338,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN XÂY DỰNG TUẤN TÚ GIA LAI</t>
+          <t>CỬA HÀNG CÔNG NGHỆ KHOA HỌC KỸ THUẬT PHAN ANH</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -9354,7 +9354,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÔNG ĐÀ 10.9</t>
+          <t>CÔNG TY TNHH NÔNG NGHIỆP NHÀ BÈ</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -9370,7 +9370,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NÔNG NGHIỆP NHÀ BÈ</t>
+          <t>CÔNG TY CỔ PHẦN SÔNG ĐÀ 10.9</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -9562,7 +9562,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>PHÒNG QUẢN LÝ ĐÔ THỊ THÀNH PHỐ PLEIKU</t>
+          <t>TRƯỜNG MẦM NON THỊ TRẤN IALY</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -9578,7 +9578,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẦM NON THỊ TRẤN IALY</t>
+          <t>PHÒNG QUẢN LÝ ĐÔ THỊ THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -9594,7 +9594,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CHATHAM CIS</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU KIỂM</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -9610,7 +9610,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU KIỂM</t>
+          <t>CÔNG TY CỔ PHẦN CHATHAM CIS</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -9642,7 +9642,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -9658,7 +9658,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -9770,7 +9770,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HỮU TÙNG GIA LAI</t>
+          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -9786,7 +9786,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
+          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -9802,7 +9802,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG PHẨM ATLANTIC VIỆT NAM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HỮU TÙNG GIA LAI</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -9818,7 +9818,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
+          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -9834,7 +9834,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
+          <t>CÔNG TY TNHH THƯƠNG PHẨM ATLANTIC VIỆT NAM</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -9978,7 +9978,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC THƯỜNG XUYÊN TỈNH GIA LAI</t>
+          <t>BẢO HIỂM XÃ HỘI TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -9994,7 +9994,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>BẢO HIỂM XÃ HỘI TỈNH GIA LAI</t>
+          <t>TRUNG TÂM GIÁO DỤC THƯỜNG XUYÊN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -10074,7 +10074,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
+          <t>TRƯỜNG TIỂU HỌC SỐ 1 IA BĂNG</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -10090,7 +10090,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC SỐ 1 IA BĂNG</t>
+          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -10122,7 +10122,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
+          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -10138,7 +10138,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
+          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -10250,7 +10250,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>HỒ ĐẮC TẤN</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -10282,7 +10282,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
+          <t>HỒ ĐẮC TẤN</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -10362,7 +10362,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN KIỆM</t>
+          <t>BAN QUẢN LÝ DỰ ÁN ĐIỆN 2 - CHI NHÁNH TẬP ĐOÀN ĐIỆN LỰC VIỆT NAM</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -10378,7 +10378,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ DỰ ÁN ĐIỆN 2 - CHI NHÁNH TẬP ĐOÀN ĐIỆN LỰC VIỆT NAM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN KIỆM</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -10490,7 +10490,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>TRƯỜNG THCS NGUYỄN CHÍ THANH</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -10506,7 +10506,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS NGUYỄN CHÍ THANH</t>
+          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -10666,7 +10666,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
+          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -10682,7 +10682,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
+          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -10714,7 +10714,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>UBND XÃ NGHĨA HÒA</t>
+          <t>CÔNG TY BẢO HIỂM PVI GIA LAI</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -10730,7 +10730,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM PVI GIA LAI</t>
+          <t>UBND XÃ NGHĨA HÒA</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -10746,7 +10746,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -10762,7 +10762,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -10810,7 +10810,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI &amp; DỊCH VỤ ĐÔNG HUY</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -10826,7 +10826,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI &amp; DỊCH VỤ ĐÔNG HUY</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -10954,7 +10954,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ H PLUS</t>
+          <t>CÔNG TY TNHH HÌNH ẢNH VIỄN ĐÔNG</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -10970,7 +10970,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HÌNH ẢNH VIỄN ĐÔNG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ H PLUS</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -11018,7 +11018,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ AN NINH ĐẤT VIỆT</t>
+          <t>CÔNG TY TNHH THIẾT BỊ Y KHOA TÂM AN</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -11034,7 +11034,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ Y KHOA TÂM AN</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ AN NINH ĐẤT VIỆT</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -11098,7 +11098,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG LUẬT SƯ HỨA HOÀNG GIA</t>
+          <t>TRƯỜNG TIỂU HỌC SỐ 1 K'DANG</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -11130,7 +11130,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC SỐ 1 K'DANG</t>
+          <t>VĂN PHÒNG LUẬT SƯ HỨA HOÀNG GIA</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -11194,7 +11194,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ GIAO HÀNG NHANH</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -11210,7 +11210,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
+          <t>CHI NHÁNH CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THỰC PHẨM GOLDSTAR TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -11226,7 +11226,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ GIAO HÀNG NHANH</t>
+          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -11242,7 +11242,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THỰC PHẨM GOLDSTAR TẠI GIA LAI</t>
+          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -11322,17 +11322,17 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>KHACH_LE</t>
+          <t>Khách lẻ</t>
         </is>
       </c>
       <c r="B682" t="n">
         <v>0</v>
       </c>
       <c r="C682" t="n">
-        <v>15592149878</v>
+        <v>15723682471</v>
       </c>
       <c r="D682" t="n">
-        <v>-15592149878</v>
+        <v>-15723682471</v>
       </c>
     </row>
   </sheetData>
@@ -11346,7 +11346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11438,7 +11438,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ĐIỀU CHỈNH XNT</t>
+          <t>Điều chỉnh XNT</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -12841,6 +12841,22 @@
       </c>
       <c r="D93" t="n">
         <v>2000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Nhà cung cấp lạ</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>22809150068.78</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-22809150068.78</v>
       </c>
     </row>
   </sheetData>

--- a/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
+++ b/docs/huyvu/sosach/nam2024/BAO_CAO_CONG_NO_2024.xlsx
@@ -3322,7 +3322,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TRƯỜNG TRUNG HỌC CƠ SỞ NGÔ GIA TỰ</t>
+          <t>BAN QUẢN LÝ DỰ ÁN - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -3338,7 +3338,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ DỰ ÁN - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>TRƯỜNG TRUNG HỌC CƠ SỞ NGÔ GIA TỰ</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -3546,7 +3546,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẠT LINH GIA LAI</t>
+          <t>CÔNG TY TNHH TƯ VẤN VÀ XÂY DỰNG DQT</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3562,7 +3562,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG GIA HUY - GIA LAI</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3578,7 +3578,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TƯ VẤN VÀ XÂY DỰNG DQT</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐẠT LINH GIA LAI</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -3594,7 +3594,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XÂY DỰNG GIA HUY - GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN THỦY ĐIỆN AN QUANG</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3674,7 +3674,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KẾ TOÁN SANG VY GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THIẾT KẾ XÂY DỰNG KIẾN XANH GIA LAI</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -3690,7 +3690,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THIẾT KẾ XÂY DỰNG KIẾN XANH GIA LAI</t>
+          <t>CÔNG TY TNHH KẾ TOÁN SANG VY GIA LAI</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3962,7 +3962,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ KON GANG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DƯỢC PHẨM PHÚ VINH GIA LAI</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -3994,7 +3994,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN DƯỢC PHẨM PHÚ VINH GIA LAI</t>
+          <t>UỶ BAN NHÂN DÂN XÃ KON GANG</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -4042,7 +4042,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC HOÀNG KIM PHÁT</t>
+          <t>CÔNG TY CỔ PHẦN TÍN THÀNH ĐẠT</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -4058,7 +4058,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TÍN THÀNH ĐẠT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC HOÀNG KIM PHÁT</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -4202,7 +4202,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ĐẢNG ỦY XÃ IA YOK</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ PVOIL MIỀN TRUNG TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -4218,7 +4218,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN XĂNG DẦU DẦU KHÍ PVOIL MIỀN TRUNG TẠI GIA LAI</t>
+          <t>CÔNG TY TNHH NHÔM KÍNH HÀ TIÊN GL</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -4234,7 +4234,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NHÔM KÍNH HÀ TIÊN GL</t>
+          <t>ĐẢNG ỦY XÃ IA YOK</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5162,7 +5162,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẪU GIÁO SAO MAI</t>
+          <t>CÔNG TY CỔ PHẦN XÂY DỰNG 711</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -5178,7 +5178,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN XÂY DỰNG 711</t>
+          <t>TRƯỜNG MẪU GIÁO SAO MAI</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -5530,7 +5530,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>LÊ THỊ LINH PHƯƠNG</t>
+          <t>Trại giống cây trồng - Binh đoàn 16</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -5546,7 +5546,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Trại giống cây trồng - Binh đoàn 16</t>
+          <t>LÊ THỊ LINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -5594,7 +5594,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TRƯỜNG THPT NGUYỄN THỊ MINH KHAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CẢNH QUANG GIA LAI</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -5610,7 +5610,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CẢNH QUANG GIA LAI</t>
+          <t>TRƯỜNG THPT NGUYỄN THỊ MINH KHAI</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -5706,7 +5706,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ĐỒN BIÊN PHÒNG IA PNÔN</t>
+          <t>CÔNG TY TNHH MTV LÂM NGHIỆP KONG H'DE</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -5738,7 +5738,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV LÂM NGHIỆP KONG H'DE</t>
+          <t>ĐỒN BIÊN PHÒNG IA PNÔN</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -5834,7 +5834,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KIẾN TRÚC XÂY DỰNG TDH</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP - GIÁO DỤC THƯỜNG XUYÊN HUYỆN CHƯ PĂH</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -5850,7 +5850,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP - GIÁO DỤC THƯỜNG XUYÊN HUYỆN CHƯ PĂH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KIẾN TRÚC XÂY DỰNG TDH</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -6026,7 +6026,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGON AVATAR - NHÀ HÀNG NGON 3 MIỀN</t>
+          <t>TRUNG TÂM HUẤN LUYỆN VÀ THI ĐẤU THỂ THAO TÍNH</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -6042,7 +6042,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HUẤN LUYỆN VÀ THI ĐẤU THỂ THAO TÍNH</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGON AVATAR - NHÀ HÀNG NGON 3 MIỀN</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -6138,7 +6138,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC LÊ HỒNG PHONG</t>
+          <t>TRUNG ĐOÀN BỘ BINH 991</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -6154,7 +6154,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TRUNG ĐOÀN BỘ BINH 991</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP -GIÁO DỤC THƯỜNG XUYÊN HUYỆN ĐAK ĐOA</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -6170,7 +6170,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP -GIÁO DỤC THƯỜNG XUYÊN HUYỆN ĐAK ĐOA</t>
+          <t>TRƯỜNG TIỂU HỌC LÊ HỒNG PHONG</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -6234,7 +6234,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KIM GIA HUY GL</t>
+          <t>LIÊN MINH HỢP TÁC XÃ TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -6250,7 +6250,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>LIÊN MINH HỢP TÁC XÃ TỈNH GIA LAI</t>
+          <t>CÔNG TY TNHH KIM GIA HUY GL</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -6362,7 +6362,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>TRUNG ĐOÀN 48</t>
+          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐĂK ĐOA</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -6378,7 +6378,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ RỪNG PHÒNG HỘ ĐĂK ĐOA</t>
+          <t>TRUNG ĐOÀN 48</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -6810,7 +6810,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG THỊNH THỦY</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ NAM PHƯƠNG GIA LAI</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -6826,7 +6826,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ NAM PHƯƠNG GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG THỊNH THỦY</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -6858,7 +6858,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TRUNG TÂM NGHIÊN CỨU CHUYỂN GIAO KỸ THUẬT TÂY NGUYÊN</t>
+          <t>UBND XÃ  Ia KhươL</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -6874,7 +6874,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>UBND XÃ  Ia KhươL</t>
+          <t>TRUNG TÂM NGHIÊN CỨU CHUYỂN GIAO KỸ THUẬT TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -7002,7 +7002,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -7018,7 +7018,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN BAKA</t>
+          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -7050,7 +7050,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>VĂN PHÒNG ĐẢNG ỦY XÃ IA TÔ</t>
+          <t>TRƯỜNG TIỂU HỌC BÙI DỰ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -7114,7 +7114,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ANDRITZ VIỆT NAM</t>
+          <t>UBND XÃ IA TÔ</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -7130,7 +7130,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HOÀNG AUTO GIA LAI</t>
+          <t>CÔNG TY TNHH ANDRITZ VIỆT NAM</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -7146,7 +7146,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>UBND XÃ IA TÔ</t>
+          <t>CÔNG TY TNHH HOÀNG AUTO GIA LAI</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -7274,7 +7274,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THIÊN PHÚ MEDICAL</t>
+          <t>BAN DÂN TỘC TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -7290,7 +7290,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>UBND THỊ TRẤN KongChro</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THIÊN PHÚ MEDICAL</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -7306,7 +7306,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BAN DÂN TỘC TỈNH GIA LAI</t>
+          <t>UBND THỊ TRẤN KongChro</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -7322,7 +7322,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -7338,7 +7338,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
+          <t>CÔNG TY TNHH MTV XÂY DỰNG CÔNG THÀNH</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -7354,7 +7354,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THUỶ ĐIỆN KÊNH BẮC - AYUN HẠ</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -7370,7 +7370,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HÀ QUÂN GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -7386,7 +7386,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN CÀ PHÊ 705</t>
+          <t>CÔNG TY CỔ PHẦN THUỶ ĐIỆN KÊNH BẮC - AYUN HẠ</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -7418,7 +7418,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV XÂY DỰNG CÔNG THÀNH</t>
+          <t>HỘ KINH DOANH VÕ THỊ PHƯƠNG THẢO</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -7450,7 +7450,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ATYCO</t>
+          <t>TRƯỜNG THCS KPA KLƠNG</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -7466,7 +7466,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS KPA KLƠNG</t>
+          <t>CÔNG TY TNHH ATYCO</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -7674,7 +7674,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO MINH GIA LAI</t>
+          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -7690,7 +7690,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TRUNG TÂM DỊCH VỤ NÔNG NGHIỆP HUYỆN IA GRAI</t>
+          <t>CÔNG TY BẢO MINH GIA LAI</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -7994,7 +7994,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CÔNG TY CP CHĂN NUÔI GIA LAI</t>
+          <t>TRƯỜNG THCS TRẦN PHÚ</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -8010,7 +8010,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -8026,7 +8026,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS TRẦN PHÚ</t>
+          <t>CÔNG TY CP CHĂN NUÔI GIA LAI</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -8042,7 +8042,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TÔN THÉP TOÀN TÍN</t>
+          <t>CƠ QUAN THƯỜNG TRỰC BÁO QUÂN ĐỘI TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -8250,7 +8250,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG SƠN 145</t>
+          <t>PHÒNG AN NINH CHÍNH TRỊ NỘI BỘ - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -8266,7 +8266,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH CHÍNH TRỊ NỘI BỘ - CÔNG AN TỈNH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG SƠN 145</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -8554,7 +8554,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN ĐIỆN GIA LAI</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -8586,7 +8586,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐIỆN GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC CƯỜNG  GIA LAI</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -8762,7 +8762,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
+          <t>TRUNG TÂM VĂN HÓA, THÔNG TIN VÀ THỂ THAO THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -8778,7 +8778,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>TRUNG TÂM VĂN HÓA, THÔNG TIN VÀ THỂ THAO THÀNH PHỐ PLEIKU</t>
+          <t>CÔNG TY CỔ PHẦN MỸ PHẨM THIÊN NHIÊN CỎ MỀM</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -8826,7 +8826,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -8842,7 +8842,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ NÔNG NGHIỆP TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XUÂN THIÊN</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -8858,7 +8858,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
+          <t>CÔNG TY TNHH DỊCH VỤ NÔNG NGHIỆP TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -8874,7 +8874,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TƯỜNG NGUYÊN GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN KỸ THUẬT LÊ THƯƠNG</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -8954,7 +8954,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>BAN QUẢN LÝ CHỢ HOA LƯ - PHÙ ĐỔNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẬU CẦN 28 SANG AN GIA LAI</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -8970,7 +8970,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH Y DƯỢC ĐỨC HẠNH GIA LAI</t>
+          <t>BAN QUẢN LÝ CHỢ HOA LƯ - PHÙ ĐỔNG</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -9002,7 +9002,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẬU CẦN 28 SANG AN GIA LAI</t>
+          <t>CÔNG TY TNHH Y DƯỢC ĐỨC HẠNH GIA LAI</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -9018,7 +9018,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG NAM ANH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN TIẾN NÔNG GIA LAI</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -9034,7 +9034,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TIẾN NÔNG GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN XÂY DỰNG NAM ANH GIA LAI</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -9066,7 +9066,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MẠNH THẮNG GLC</t>
+          <t>CÔNG TY TNHH BÁCH CÁT NGUYÊN</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -9082,7 +9082,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>VNPT GIA LAI</t>
+          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -9098,7 +9098,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>SỞ GIAO THÔNG VẬN TẢI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN MẠNH THẮNG GLC</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -9114,7 +9114,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BÁCH CÁT NGUYÊN</t>
+          <t>VNPT GIA LAI</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -9210,7 +9210,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>LIÊN ĐOÀN BÓNG ĐÁ VIỆT NAM</t>
+          <t>KHO K896/CQK</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -9242,7 +9242,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>KHO K896/CQK</t>
+          <t>LIÊN ĐOÀN BÓNG ĐÁ VIỆT NAM</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -9562,7 +9562,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>TRƯỜNG MẦM NON THỊ TRẤN IALY</t>
+          <t>PHÒNG QUẢN LÝ ĐÔ THỊ THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -9578,7 +9578,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>PHÒNG QUẢN LÝ ĐÔ THỊ THÀNH PHỐ PLEIKU</t>
+          <t>TRƯỜNG MẦM NON THỊ TRẤN IALY</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -9594,7 +9594,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU KIỂM</t>
+          <t>CÔNG TY CỔ PHẦN CHATHAM CIS</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -9610,7 +9610,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CHATHAM CIS</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CHÂU KIỂM</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -9642,7 +9642,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -9658,7 +9658,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN SÂM KBC</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NĂNG LƯỢNG SẠCH HOÀNG GIA THỊNH</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -9706,7 +9706,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS IALY</t>
+          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP 3T GIA LAI</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -9722,7 +9722,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC NGHỀ NGHIỆP 3T GIA LAI</t>
+          <t>TRƯỜNG THCS IALY</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -9770,7 +9770,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
+          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -9786,7 +9786,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
+          <t>Công ty TNHH MTV Thiết Bị Y Tế Thanh Lộc Phát</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -9802,7 +9802,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HỮU TÙNG GIA LAI</t>
+          <t>TRUNG TÂM HẠ TẦNG MIỀN TRUNG</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -9818,7 +9818,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Đảng ủy xã nghĩa hòa huyện chư pah gia lai</t>
+          <t>CÔNG TY TNHH THƯƠNG PHẨM ATLANTIC VIỆT NAM</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -9834,7 +9834,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG PHẨM ATLANTIC VIỆT NAM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HỮU TÙNG GIA LAI</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -9866,7 +9866,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>CỤM 2287 - BTM - QUÂN KHU 5</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC SÊ</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -9882,7 +9882,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC SÊ</t>
+          <t>CỤM 2287 - BTM - QUÂN KHU 5</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -9946,7 +9946,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH RED RIVER FOODS VIỆT NAM TẠI GIA LAI</t>
+          <t>HỘI ĐỒNG NHÂN DÂN PHƯỜNG HỘI THƯƠNG</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -9962,7 +9962,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>HỘI ĐỒNG NHÂN DÂN PHƯỜNG HỘI THƯƠNG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH RED RIVER FOODS VIỆT NAM TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -9978,7 +9978,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>BẢO HIỂM XÃ HỘI TỈNH GIA LAI</t>
+          <t>TRUNG TÂM GIÁO DỤC THƯỜNG XUYÊN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -9994,7 +9994,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>TRUNG TÂM GIÁO DỤC THƯỜNG XUYÊN TỈNH GIA LAI</t>
+          <t>BẢO HIỂM XÃ HỘI TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -10058,7 +10058,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THT TÂY NGUYÊN</t>
+          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -10074,7 +10074,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>TRƯỜNG TIỂU HỌC SỐ 1 IA BĂNG</t>
+          <t>CÔNG TY TNHH THT TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -10090,7 +10090,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>TỔNG CÔNG TY CÀ PHÊ VIỆT NAM – CÔNG TY TNHH MỘT THÀNH VIÊN</t>
+          <t>TRƯỜNG TIỂU HỌC SỐ 1 IA BĂNG</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -10122,7 +10122,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
+          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -10138,7 +10138,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CP TM CHUYỂN PHÁT NHANH EPS</t>
+          <t>CÔNG TY TNHH THIÊN PHÚC ĐAN</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -10218,7 +10218,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN Ô TÔ BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH Ô TÔ MG GIA LAI</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -10234,7 +10234,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH Ô TÔ MG GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN Ô TÔ BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -10250,7 +10250,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
+          <t>UBND XÃ IA BĂNG</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -10266,7 +10266,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>UBND XÃ IA BĂNG</t>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN TÀI CHÍNH VÀ PHÁT TRIỂN DOANH NGHIỆP TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -10410,7 +10410,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÓNG ĐÈN PHÍCH NƯỚC RẠNG ĐÔNG CHI NHÁNH TÂY NGUYÊN</t>
+          <t>CÔNG AN THÀNH PHỐ PLEIKU</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -10442,7 +10442,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>CÔNG AN THÀNH PHỐ PLEIKU</t>
+          <t>CÔNG TY CỔ PHẦN BÓNG ĐÈN PHÍCH NƯỚC RẠNG ĐÔNG CHI NHÁNH TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -10506,7 +10506,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
+          <t>CÔNG TY CỔ PHẦN ĐỊNH GIÁ VÀ DỊCH VỤ TÀI CHÍNH HOÀNG CẦU</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -10522,7 +10522,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐỊNH GIÁ VÀ DỊCH VỤ TÀI CHÍNH HOÀNG CẦU</t>
+          <t>PHÒNG CHÍNH TRỊ - BỘ THAM MƯU - QUÂN ĐOÀN 3</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -10570,7 +10570,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>UỶ BAN NHÂN DÂN XÃ GÀO</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ CHUYÊN NGHIỆP HÂN NAM</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -10586,7 +10586,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ BẢO VỆ CHUYÊN NGHIỆP HÂN NAM</t>
+          <t>UỶ BAN NHÂN DÂN XÃ GÀO</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -10666,7 +10666,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
+          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -10682,7 +10682,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>PHÒNG AN NINH MẠNG VÀ PCTP SỬ DỤNG CÔNG NGHỆ CAO - CÔNG AN TỈNH GIA LAI</t>
+          <t>CHI NHÁNH VẬN TẢI VÀ THI CÔNG CƠ GIỚI - TỔNG CÔNG TY XÂY DỰNG LŨNG LÔ</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -10746,7 +10746,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -10762,7 +10762,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ Ô TÔ HẢI ÂU</t>
+          <t>CÔNG TY CỔ PHẦN CẤP NƯỚC SÀI GÒN - PLEIKU</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -10810,7 +10810,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI &amp; DỊCH VỤ ĐÔNG HUY</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -10826,7 +10826,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI &amp; DỊCH VỤ ĐÔNG HUY</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -10858,7 +10858,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CỘNG ĐỒNG XE TẢI VIỆT NAM – CHI NHÁNH GIA LAI</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY THƯƠNG MẠI KỸ THUẬT VÀ ĐẦU TƯ - CÔNG TY CỔ PHẦN TẠI TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -10874,7 +10874,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY THƯƠNG MẠI KỸ THUẬT VÀ ĐẦU TƯ - CÔNG TY CỔ PHẦN TẠI TỈNH GIA LAI</t>
+          <t>TRUNG TÂM XỬ LÝ BOM MÌN VÀ MÔI TRƯỜNG</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -10890,7 +10890,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>TRUNG TÂM XỬ LÝ BOM MÌN VÀ MÔI TRƯỜNG</t>
+          <t>CÔNG TY CỔ PHẦN CỘNG ĐỒNG XE TẢI VIỆT NAM – CHI NHÁNH GIA LAI</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -11114,7 +11114,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>PA 05, CÔNG AN TỈNH GIA LAI</t>
+          <t>TRƯỜNG THCS NGUYỄN VIẾT XUÂN</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -11146,7 +11146,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>CHI NHÁNH GIA LAI - TP.PLEIKU 3 - CÔNG TY CỔ PHẦN SAWAD TIỀN CÓ NGAY</t>
+          <t>PA 05, CÔNG AN TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -11162,7 +11162,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>TRƯỜNG THCS NGUYỄN VIẾT XUÂN</t>
+          <t>CHI NHÁNH GIA LAI - TP.PLEIKU 3 - CÔNG TY CỔ PHẦN SAWAD TIỀN CÓ NGAY</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -11194,7 +11194,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DỊCH VỤ GIAO HÀNG NHANH</t>
+          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -11210,7 +11210,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THỰC PHẨM GOLDSTAR TẠI GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -11226,7 +11226,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN HỌC VIỆN CAFE VIỆT NAM VCA</t>
+          <t>CHI NHÁNH CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ THỰC PHẨM GOLDSTAR TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -11242,7 +11242,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Công Đoàn Trường Tiểu Học Hoàng Hoa Thám</t>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ GIAO HÀNG NHANH</t>
         </is>
       </c>
       <c r="B677" t="n">
